--- a/005/xy_005_data.xlsx
+++ b/005/xy_005_data.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/005/xy_005_data.xlsx
+++ b/005/xy_005_data.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Every extra three a game buys the league about a point.</t>
+          <t>Teams that take more of their shots as threes score more per possession.</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scoring bottomed near 17 three-point attempts per game, then rose.</t>
+          <t>Efficiency is highest in the three-point era, but not in a straight line.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3PA per game (NBA league avg)</t>
+          <t>Share of shots that are threes (%, NBA)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Three-point attempts per team per game, NBA league average by season, Basketball Reference, 1979-80 - present</t>
+          <t>Three-point attempts as a share of all field-goal attempts, NBA league average by season, Basketball Reference, 1979-80 - present</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Points per game (NBA league avg)</t>
+          <t>Points per 100 possessions (NBA)</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Points per team per game, NBA league average by season, Basketball Reference, 1979-80 - present</t>
+          <t>Offensive rating, points per 100 possessions, NBA league average by season, Basketball Reference, 1979-80 - present</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -803,12 +803,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3PA per game (NBA league avg)</t>
+          <t>Share of shots that are threes (%, NBA)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Points per game (NBA league avg)</t>
+          <t>Points per 100 possessions (NBA)</t>
         </is>
       </c>
     </row>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>41.5263748597082</v>
       </c>
       <c r="C2" t="n">
-        <v>115.6</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="3">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.6</v>
+        <v>42.152466367713</v>
       </c>
       <c r="C3" t="n">
-        <v>113.8</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="4">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.1</v>
+        <v>39.48256467941507</v>
       </c>
       <c r="C4" t="n">
-        <v>114.2</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="5">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.2</v>
+        <v>38.73159682899207</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="6">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.2</v>
+        <v>39.95459704880817</v>
       </c>
       <c r="C6" t="n">
-        <v>110.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.6</v>
+        <v>39.14027149321267</v>
       </c>
       <c r="C7" t="n">
-        <v>112.1</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="8">
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.1</v>
+        <v>38.4009009009009</v>
       </c>
       <c r="C8" t="n">
-        <v>111.8</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="9">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>35.87443946188341</v>
       </c>
       <c r="C9" t="n">
-        <v>111.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="10">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>33.68176538908246</v>
       </c>
       <c r="C10" t="n">
-        <v>106.3</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="11">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>31.615925058548</v>
       </c>
       <c r="C11" t="n">
-        <v>105.6</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="12">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.1</v>
+        <v>28.48699763593381</v>
       </c>
       <c r="C12" t="n">
-        <v>102.7</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="13">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.4</v>
+        <v>26.79425837320574</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="14">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.5</v>
+        <v>25.90361445783132</v>
       </c>
       <c r="C14" t="n">
-        <v>101</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="15">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>24.39024390243902</v>
       </c>
       <c r="C15" t="n">
-        <v>98.09999999999999</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="16">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.4</v>
+        <v>22.6044226044226</v>
       </c>
       <c r="C16" t="n">
-        <v>96.3</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="17">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>22.16748768472906</v>
       </c>
       <c r="C17" t="n">
-        <v>99.59999999999999</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="18">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.1</v>
+        <v>22.15422276621787</v>
       </c>
       <c r="C18" t="n">
-        <v>100.4</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="19">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.1</v>
+        <v>22.37330037082818</v>
       </c>
       <c r="C19" t="n">
-        <v>100</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="20">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18.1</v>
+        <v>22.20858895705522</v>
       </c>
       <c r="C20" t="n">
-        <v>99.90000000000001</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="21">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.9</v>
+        <v>21.20451693851945</v>
       </c>
       <c r="C21" t="n">
-        <v>98.7</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="22">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>20.25316455696203</v>
       </c>
       <c r="C22" t="n">
-        <v>97</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="23">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.8</v>
+        <v>19.67621419676214</v>
       </c>
       <c r="C23" t="n">
-        <v>97.2</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="24">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.9</v>
+        <v>18.67167919799499</v>
       </c>
       <c r="C24" t="n">
-        <v>93.40000000000001</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="25">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.7</v>
+        <v>18.19306930693069</v>
       </c>
       <c r="C25" t="n">
-        <v>95.09999999999999</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="26">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.7</v>
+        <v>18.08118081180812</v>
       </c>
       <c r="C26" t="n">
-        <v>95.5</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="27">
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.7</v>
+        <v>16.99751861042184</v>
       </c>
       <c r="C27" t="n">
-        <v>94.8</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13.7</v>
+        <v>16.68696711327649</v>
       </c>
       <c r="C28" t="n">
-        <v>97.5</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="29">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13.2</v>
+        <v>16.87979539641944</v>
       </c>
       <c r="C29" t="n">
-        <v>91.59999999999999</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="30">
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12.7</v>
+        <v>15.93475533249686</v>
       </c>
       <c r="C30" t="n">
-        <v>95.59999999999999</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.8</v>
+        <v>21.18537200504414</v>
       </c>
       <c r="C31" t="n">
-        <v>96.90000000000001</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="32">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>19.9501246882793</v>
       </c>
       <c r="C32" t="n">
-        <v>99.5</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="33">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.3</v>
+        <v>18.77300613496933</v>
       </c>
       <c r="C33" t="n">
-        <v>101.4</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="34">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9.9</v>
+        <v>11.72985781990521</v>
       </c>
       <c r="C34" t="n">
-        <v>101.5</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="35">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>10.46511627906977</v>
       </c>
       <c r="C35" t="n">
-        <v>105.3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7.6</v>
+        <v>8.705612829324169</v>
       </c>
       <c r="C36" t="n">
-        <v>105.3</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="37">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7.1</v>
+        <v>8.142201834862385</v>
       </c>
       <c r="C37" t="n">
-        <v>106.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="38">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.6</v>
+        <v>7.56880733944954</v>
       </c>
       <c r="C38" t="n">
-        <v>107</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="39">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6.6</v>
+        <v>7.41573033707865</v>
       </c>
       <c r="C39" t="n">
-        <v>109.2</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="40">
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>5.701254275940706</v>
       </c>
       <c r="C40" t="n">
-        <v>108.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.7</v>
+        <v>5.292792792792793</v>
       </c>
       <c r="C41" t="n">
-        <v>109.9</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="42">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.3</v>
+        <v>3.724604966139955</v>
       </c>
       <c r="C42" t="n">
-        <v>110.2</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="43">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.1</v>
+        <v>3.479236812570146</v>
       </c>
       <c r="C43" t="n">
-        <v>110.8</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="44">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.4</v>
+        <v>2.714932126696832</v>
       </c>
       <c r="C44" t="n">
-        <v>110.1</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="45">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.3</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="C45" t="n">
-        <v>108.5</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="46">
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.3</v>
+        <v>2.607709750566893</v>
       </c>
       <c r="C46" t="n">
-        <v>108.6</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="47">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>2.262443438914027</v>
       </c>
       <c r="C47" t="n">
-        <v>108.1</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="48">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.8</v>
+        <v>3.090507726269316</v>
       </c>
       <c r="C48" t="n">
-        <v>109.3</v>
+        <v>105.3</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1438,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3PA per game (NBA league avg)</t>
+          <t>Share of shots that are threes (%, NBA)</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>41.5263748597082</v>
       </c>
     </row>
     <row r="3">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.6</v>
+        <v>42.152466367713</v>
       </c>
     </row>
     <row r="4">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.1</v>
+        <v>39.48256467941507</v>
       </c>
     </row>
     <row r="5">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.2</v>
+        <v>38.73159682899207</v>
       </c>
     </row>
     <row r="6">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.2</v>
+        <v>39.95459704880817</v>
       </c>
     </row>
     <row r="7">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.6</v>
+        <v>39.14027149321267</v>
       </c>
     </row>
     <row r="8">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.1</v>
+        <v>38.4009009009009</v>
       </c>
     </row>
     <row r="9">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>35.87443946188341</v>
       </c>
     </row>
     <row r="10">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>33.68176538908246</v>
       </c>
     </row>
     <row r="11">
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>31.615925058548</v>
       </c>
     </row>
     <row r="12">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.1</v>
+        <v>28.48699763593381</v>
       </c>
     </row>
     <row r="13">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.4</v>
+        <v>26.79425837320574</v>
       </c>
     </row>
     <row r="14">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.5</v>
+        <v>25.90361445783132</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>24.39024390243902</v>
       </c>
     </row>
     <row r="16">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18.4</v>
+        <v>22.6044226044226</v>
       </c>
     </row>
     <row r="17">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>22.16748768472906</v>
       </c>
     </row>
     <row r="18">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.1</v>
+        <v>22.15422276621787</v>
       </c>
     </row>
     <row r="19">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.1</v>
+        <v>22.37330037082818</v>
       </c>
     </row>
     <row r="20">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18.1</v>
+        <v>22.20858895705522</v>
       </c>
     </row>
     <row r="21">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.9</v>
+        <v>21.20451693851945</v>
       </c>
     </row>
     <row r="22">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>20.25316455696203</v>
       </c>
     </row>
     <row r="23">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.8</v>
+        <v>19.67621419676214</v>
       </c>
     </row>
     <row r="24">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.9</v>
+        <v>18.67167919799499</v>
       </c>
     </row>
     <row r="25">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.7</v>
+        <v>18.19306930693069</v>
       </c>
     </row>
     <row r="26">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.7</v>
+        <v>18.08118081180812</v>
       </c>
     </row>
     <row r="27">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.7</v>
+        <v>16.99751861042184</v>
       </c>
     </row>
     <row r="28">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13.7</v>
+        <v>16.68696711327649</v>
       </c>
     </row>
     <row r="29">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13.2</v>
+        <v>16.87979539641944</v>
       </c>
     </row>
     <row r="30">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12.7</v>
+        <v>15.93475533249686</v>
       </c>
     </row>
     <row r="31">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.8</v>
+        <v>21.18537200504414</v>
       </c>
     </row>
     <row r="32">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>19.9501246882793</v>
       </c>
     </row>
     <row r="33">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.3</v>
+        <v>18.77300613496933</v>
       </c>
     </row>
     <row r="34">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9.9</v>
+        <v>11.72985781990521</v>
       </c>
     </row>
     <row r="35">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>10.46511627906977</v>
       </c>
     </row>
     <row r="36">
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7.6</v>
+        <v>8.705612829324169</v>
       </c>
     </row>
     <row r="37">
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7.1</v>
+        <v>8.142201834862385</v>
       </c>
     </row>
     <row r="38">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6.6</v>
+        <v>7.56880733944954</v>
       </c>
     </row>
     <row r="39">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6.6</v>
+        <v>7.41573033707865</v>
       </c>
     </row>
     <row r="40">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>5.701254275940706</v>
       </c>
     </row>
     <row r="41">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.7</v>
+        <v>5.292792792792793</v>
       </c>
     </row>
     <row r="42">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.3</v>
+        <v>3.724604966139955</v>
       </c>
     </row>
     <row r="43">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.1</v>
+        <v>3.479236812570146</v>
       </c>
     </row>
     <row r="44">
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.4</v>
+        <v>2.714932126696832</v>
       </c>
     </row>
     <row r="45">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.3</v>
+        <v>2.564102564102564</v>
       </c>
     </row>
     <row r="46">
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.3</v>
+        <v>2.607709750566893</v>
       </c>
     </row>
     <row r="47">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>2.262443438914027</v>
       </c>
     </row>
     <row r="48">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.8</v>
+        <v>3.090507726269316</v>
       </c>
     </row>
   </sheetData>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Points per game (NBA league avg)</t>
+          <t>Points per 100 possessions (NBA)</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115.6</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="3">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113.8</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="4">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>114.2</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="5">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="6">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.1</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="8">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111.8</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="9">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="10">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106.3</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="11">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105.6</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="12">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102.7</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="13">
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="14">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>101</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="15">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98.09999999999999</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="16">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>96.3</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="17">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.59999999999999</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="18">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100.4</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="19">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>100</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="20">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>99.90000000000001</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="21">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>98.7</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="22">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>97</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="23">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>97.2</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="24">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93.40000000000001</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="25">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95.09999999999999</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="26">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>95.5</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="27">
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>94.8</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>97.5</v>
+        <v>104.1</v>
       </c>
     </row>
     <row r="29">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91.59999999999999</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="30">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95.59999999999999</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>96.90000000000001</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="32">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>99.5</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="33">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>101.4</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="34">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>101.5</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="35">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>105.3</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>105.3</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="37">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>106.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="38">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>107</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="39">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>109.2</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="40">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>108.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>109.9</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="42">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>110.2</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="43">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>110.8</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="44">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>110.1</v>
+        <v>107.6</v>
       </c>
     </row>
     <row r="45">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>108.5</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="46">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>108.6</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="47">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>108.1</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="48">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>109.3</v>
+        <v>105.3</v>
       </c>
     </row>
   </sheetData>
@@ -2438,7 +2438,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2482,14 +2482,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.133539, 101.74</t>
+          <t>0.154518, 104.555</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.0475</v>
+        <v>0.3617</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0263</v>
+        <v>0.3476</v>
       </c>
     </row>
     <row r="3">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.050939, -1.81942, 114.394</t>
+          <t>0.0128393, -0.392566, 108.486</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.838</v>
+        <v>0.7294</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8306</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="4">
@@ -2524,14 +2524,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.000991195, 0.106666, -2.63178, 116.906</t>
+          <t>0.000410961, -0.0136039, 0.0533643, 106.943</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.7527</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8431</v>
+        <v>0.7355</v>
       </c>
     </row>
     <row r="5">
@@ -2545,14 +2545,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.000143425, 0.0100414, -0.170459, -0.116524, 111.206</t>
+          <t>-2.91943e-05, 0.00293263, -0.0848603, 0.783931, 105.08</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8854</v>
+        <v>0.768</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8744</v>
+        <v>0.7459</v>
       </c>
     </row>
     <row r="6">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2179</v>
+        <v>0.6014</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1412721728186427</v>
+        <v>7.784184867919516e-06</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4376793929983442</v>
+        <v>0.01020115991237892</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>y = 0.134x + 102</t>
+          <t>y = 0.155x + 105</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>

--- a/005/xy_005_data.xlsx
+++ b/005/xy_005_data.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Math Ruined Basketball. Or Saved It.</t>
+          <t>Three-Point Share vs Scoring Efficiency</t>
         </is>
       </c>
     </row>
@@ -484,293 +484,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Teams that take more of their shots as threes score more per possession.</t>
+          <t>More threes, more points per possession.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Efficiency is highest in the three-point era, but not in a straight line.</t>
+          <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://xandyregression.substack.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Share of shots that are threes (%, NBA)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Share of shots that are threes (%, NBA)</t>
+          <t>Three-point attempts as a share of all field-goal attempts, NBA league average by season, Basketball Reference, 1979-80 - present</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Three-point attempts as a share of all field-goal attempts, NBA league average by season, Basketball Reference, 1979-80 - present</t>
+          <t>Basketball Reference league per-game averages</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Basketball Reference league per-game averages</t>
+          <t>https://www.basketball-reference.com/leagues/NBA_stats_per_game.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.basketball-reference.com/leagues/NBA_stats_per_game.html</t>
+          <t>third-party data: only the aggregated values used are included, see source</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>third-party data: only the aggregated values used are included, see source</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>X steps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X steps</t>
+          <t>X raw sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>values used in the regression only (source licence); full series at source URL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>X raw sheet</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>values used in the regression only (source licence); full series at source URL</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Points per 100 possessions (NBA)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y label</t>
+          <t>Y detail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Points per 100 possessions (NBA)</t>
+          <t>Offensive rating, points per 100 possessions, NBA league average by season, Basketball Reference, 1979-80 - present</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y detail</t>
+          <t>Y source</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Offensive rating, points per 100 possessions, NBA league average by season, Basketball Reference, 1979-80 - present</t>
+          <t>Basketball Reference league per-game averages</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y source</t>
+          <t>Y source URL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Basketball Reference league per-game averages</t>
+          <t>https://www.basketball-reference.com/leagues/NBA_stats_per_game.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y source URL</t>
+          <t>Y licence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.basketball-reference.com/leagues/NBA_stats_per_game.html</t>
+          <t>third-party data: only the aggregated values used are included, see source</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y licence</t>
+          <t>Y pulled</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>third-party data: only the aggregated values used are included, see source</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y pulled</t>
+          <t>Y steps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y steps</t>
+          <t>Y raw sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>values used in the regression only (source licence); full series at source URL</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Y raw sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>values used in the regression only (source licence); full series at source URL</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>join</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>on key</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>join</t>
+          <t>lag</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>on key</t>
+          <t>X leads Y by 0 periods</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lag</t>
+          <t>transform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>X leads Y by 0 periods</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Newey-West (HAC) for time series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
-        <is>
-          <t>Newey-West (HAC) for time series</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
